--- a/Dataset2.xlsx
+++ b/Dataset2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MyBook Z Series\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE1DF1F8-E587-4E51-83BF-B72048C31855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29A2431C-C8DC-48D4-AEAD-47838D933741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0EAB97F0-0957-4D9B-B7FD-20E7CE86B6C9}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="91">
   <si>
     <t>T1</t>
   </si>
@@ -99,18 +99,6 @@
     <t>T24</t>
   </si>
   <si>
-    <t>T25</t>
-  </si>
-  <si>
-    <t>T26</t>
-  </si>
-  <si>
-    <t>T27</t>
-  </si>
-  <si>
-    <t>T28</t>
-  </si>
-  <si>
     <t>Nama_Titik</t>
   </si>
   <si>
@@ -168,172 +156,148 @@
     <t>Rendah</t>
   </si>
   <si>
-    <t>108°02'34.60"</t>
-  </si>
-  <si>
-    <t>7°20'31.40"</t>
-  </si>
-  <si>
-    <t>108°02'34.55"</t>
-  </si>
-  <si>
-    <t>7°20'31.53"</t>
-  </si>
-  <si>
     <t>7°20'31.55"</t>
   </si>
   <si>
-    <t>7°20'31.61"</t>
-  </si>
-  <si>
-    <t>7°20'31.67"</t>
-  </si>
-  <si>
     <t>7°20'31.74"</t>
   </si>
   <si>
-    <t>7°20'31.76"</t>
-  </si>
-  <si>
-    <t>7°20'31.82"</t>
-  </si>
-  <si>
-    <t>7°20'31.91"</t>
-  </si>
-  <si>
-    <t>7°20'32.04"</t>
-  </si>
-  <si>
-    <t>108°02'34.45"</t>
-  </si>
-  <si>
-    <t>7°20'32.18"</t>
-  </si>
-  <si>
-    <t>108°02'34.75"</t>
-  </si>
-  <si>
-    <t>108°02'34.38"</t>
-  </si>
-  <si>
-    <t>108°02'34.53"</t>
-  </si>
-  <si>
-    <t>108°02'34.68"</t>
-  </si>
-  <si>
-    <t>108°02'34.32"</t>
-  </si>
-  <si>
-    <t>108°02'34.47"</t>
-  </si>
-  <si>
-    <t>7°20'31.80"</t>
-  </si>
-  <si>
-    <t>7°20'31.95"</t>
-  </si>
-  <si>
-    <t>7°20'32.10"</t>
-  </si>
-  <si>
-    <t>108°02'34.69"</t>
-  </si>
-  <si>
-    <t>108°02'34.90"</t>
-  </si>
-  <si>
-    <t>108°02'34.84"</t>
-  </si>
-  <si>
-    <t>108°02'35.05"</t>
-  </si>
-  <si>
-    <t>108°02'34.99"</t>
-  </si>
-  <si>
-    <t>108°02'35.14"</t>
-  </si>
-  <si>
-    <t>7°20'31.69"</t>
-  </si>
-  <si>
     <t>7°20'31.84"</t>
   </si>
   <si>
-    <t>108°02'34.25"</t>
-  </si>
-  <si>
-    <t>7°20'31.47"</t>
-  </si>
-  <si>
-    <t>108°02'34.40"</t>
-  </si>
-  <si>
-    <t>7°20'31.68"</t>
-  </si>
-  <si>
     <t>7°20'31.83"</t>
   </si>
   <si>
-    <t>108°02'34.61"</t>
-  </si>
-  <si>
-    <t>7°20'31.98"</t>
-  </si>
-  <si>
-    <t>7°20'31.60"</t>
-  </si>
-  <si>
     <t>7°20'31.75"</t>
   </si>
   <si>
-    <t>108°02'34.83"</t>
-  </si>
-  <si>
     <t>7°20'31.90"</t>
   </si>
   <si>
-    <t>108°02'34.76"</t>
-  </si>
-  <si>
-    <t>108°02'34.98"</t>
-  </si>
-  <si>
-    <t>7°20'31.96"</t>
-  </si>
-  <si>
-    <t>108°02'34.91"</t>
-  </si>
-  <si>
     <t>7°20'32.11"</t>
   </si>
   <si>
-    <t>108°02'35.19"</t>
-  </si>
-  <si>
-    <t>7°20'31.88"</t>
-  </si>
-  <si>
-    <t>108°02'35.13"</t>
-  </si>
-  <si>
     <t>7°20'32.03"</t>
   </si>
   <si>
-    <t>108°02'35.06"</t>
-  </si>
-  <si>
-    <t>108°02'35.34"</t>
-  </si>
-  <si>
-    <t>108°02'35.27"</t>
-  </si>
-  <si>
-    <t>108°02'35.21"</t>
-  </si>
-  <si>
-    <t>7°20'32.24"</t>
+    <t>7°20'31.30"</t>
+  </si>
+  <si>
+    <t>108°2'34.38"</t>
+  </si>
+  <si>
+    <t>7°20'31.49"</t>
+  </si>
+  <si>
+    <t>108°2'34.29"</t>
+  </si>
+  <si>
+    <t>7°20'31.66"</t>
+  </si>
+  <si>
+    <t>108°2'34.22"</t>
+  </si>
+  <si>
+    <t>7°20'31.85"</t>
+  </si>
+  <si>
+    <t>108°2'34.13"</t>
+  </si>
+  <si>
+    <t>7°20'31.39"</t>
+  </si>
+  <si>
+    <t>108°2'34.57"</t>
+  </si>
+  <si>
+    <t>7°20'31.56"</t>
+  </si>
+  <si>
+    <t>108°2'34.48"</t>
+  </si>
+  <si>
+    <t>108°2'34.40"</t>
+  </si>
+  <si>
+    <t>7°20'31.94"</t>
+  </si>
+  <si>
+    <t>108°2'34.32"</t>
+  </si>
+  <si>
+    <t>7°20'31.46"</t>
+  </si>
+  <si>
+    <t>108°2'34.76"</t>
+  </si>
+  <si>
+    <t>7°20'31.65"</t>
+  </si>
+  <si>
+    <t>108°2'34.67"</t>
+  </si>
+  <si>
+    <t>108°2'34.58"</t>
+  </si>
+  <si>
+    <t>108°2'34.51"</t>
+  </si>
+  <si>
+    <t>108°2'34.95"</t>
+  </si>
+  <si>
+    <t>108°2'34.86"</t>
+  </si>
+  <si>
+    <t>7°20'31.93"</t>
+  </si>
+  <si>
+    <t>108°2'34.77"</t>
+  </si>
+  <si>
+    <t>108°2'34.68"</t>
+  </si>
+  <si>
+    <t>7°20'31.64"</t>
+  </si>
+  <si>
+    <t>108°2'35.14"</t>
+  </si>
+  <si>
+    <t>108°2'35.05"</t>
+  </si>
+  <si>
+    <t>7°20'32.00"</t>
+  </si>
+  <si>
+    <t>108°2'34.96"</t>
+  </si>
+  <si>
+    <t>7°20'32.19"</t>
+  </si>
+  <si>
+    <t>108°2'34.87"</t>
+  </si>
+  <si>
+    <t>7°20'31.73"</t>
+  </si>
+  <si>
+    <t>108°2'35.31"</t>
+  </si>
+  <si>
+    <t>108°2'35.24"</t>
+  </si>
+  <si>
+    <t>7°20'32.09"</t>
+  </si>
+  <si>
+    <t>108°2'35.15"</t>
+  </si>
+  <si>
+    <t>7°20'32.28"</t>
+  </si>
+  <si>
+    <t>108°2'35.06"</t>
   </si>
 </sst>
 </file>
@@ -399,7 +363,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -412,6 +376,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -729,7 +696,9 @@
   <dimension ref="A1:M29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.33203125" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.5546875" bestFit="1" customWidth="1"/>
@@ -745,43 +714,43 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -789,28 +758,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D2" s="4">
         <v>86.98</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F2" s="4">
         <v>54.43</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H2" s="4">
         <v>79.39</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J2" s="4">
         <v>6.9</v>
@@ -822,7 +791,7 @@
         <v>23.1</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -830,28 +799,28 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D3" s="4">
         <v>82.33</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F3" s="4">
         <v>47.03</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H3" s="4">
         <v>87.02</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J3" s="4">
         <v>6.7</v>
@@ -863,7 +832,7 @@
         <v>22.9</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -871,28 +840,28 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D4" s="4">
         <v>73.260000000000005</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F4" s="4">
         <v>38.119999999999997</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H4" s="4">
         <v>97.5</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J4" s="4">
         <v>6.4</v>
@@ -904,7 +873,7 @@
         <v>23.4</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
@@ -912,28 +881,28 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="D5" s="4">
         <v>91.24</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F5" s="4">
         <v>47.36</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H5" s="4">
         <v>90.67</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J5" s="4">
         <v>6.3</v>
@@ -945,7 +914,7 @@
         <v>22.4</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
@@ -953,28 +922,28 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="D6" s="4">
         <v>86.52</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F6" s="4">
         <v>50.65</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H6" s="4">
         <v>83.92</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J6" s="4">
         <v>6.4</v>
@@ -986,7 +955,7 @@
         <v>22.2</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
@@ -994,28 +963,28 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D7" s="4">
         <v>93.77</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F7" s="4">
         <v>48.86</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H7" s="4">
         <v>94.9</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J7" s="4">
         <v>6.5</v>
@@ -1027,7 +996,7 @@
         <v>23.1</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
@@ -1035,28 +1004,28 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D8" s="4">
         <v>81.5</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F8" s="4">
         <v>45.64</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H8" s="4">
         <v>80.83</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J8" s="4">
         <v>7</v>
@@ -1068,7 +1037,7 @@
         <v>22.1</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
@@ -1076,28 +1045,28 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="D9" s="4">
         <v>94.24</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F9" s="4">
         <v>41.96</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H9" s="4">
         <v>76.28</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J9" s="4">
         <v>6.2</v>
@@ -1109,7 +1078,7 @@
         <v>22.7</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
@@ -1117,28 +1086,28 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D10" s="4">
         <v>80.88</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F10" s="4">
         <v>45.13</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H10" s="4">
         <v>94.54</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J10" s="4">
         <v>6.4</v>
@@ -1150,7 +1119,7 @@
         <v>23.7</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
@@ -1158,28 +1127,28 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D11" s="4">
         <v>77.430000000000007</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F11" s="4">
         <v>52.43</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H11" s="4">
         <v>81.88</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J11" s="4">
         <v>6.5</v>
@@ -1191,7 +1160,7 @@
         <v>23.9</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
@@ -1199,28 +1168,28 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D12" s="4">
         <v>93.16</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F12" s="4">
         <v>42.57</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H12" s="4">
         <v>83.09</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J12" s="4">
         <v>6.1</v>
@@ -1232,7 +1201,7 @@
         <v>23.4</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
@@ -1240,28 +1209,28 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="D13" s="4">
         <v>68.7</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F13" s="4">
         <v>36.94</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H13" s="4">
         <v>83.83</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J13" s="4">
         <v>6.2</v>
@@ -1273,7 +1242,7 @@
         <v>23.2</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
@@ -1281,28 +1250,28 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D14" s="4">
         <v>48.4</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F14" s="4">
         <v>36.07</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H14" s="4">
         <v>80.349999999999994</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J14" s="4">
         <v>6</v>
@@ -1314,7 +1283,7 @@
         <v>22.9</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
@@ -1322,28 +1291,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="D15" s="4">
         <v>65.400000000000006</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F15" s="4">
         <v>41.98</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H15" s="4">
         <v>55.36</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J15" s="4">
         <v>6.3</v>
@@ -1355,7 +1324,7 @@
         <v>22.5</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
@@ -1363,28 +1332,28 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="D16" s="4">
         <v>60.35</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F16" s="4">
         <v>47.6</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H16" s="4">
         <v>80.400000000000006</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J16" s="4">
         <v>7.5</v>
@@ -1396,7 +1365,7 @@
         <v>22.9</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
@@ -1404,28 +1373,28 @@
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D17" s="4">
         <v>64.55</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F17" s="4">
         <v>36.47</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H17" s="4">
         <v>75.069999999999993</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J17" s="4">
         <v>7.4</v>
@@ -1437,7 +1406,7 @@
         <v>22.6</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
@@ -1445,28 +1414,28 @@
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D18" s="4">
         <v>50.59</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F18" s="4">
         <v>46.84</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H18" s="4">
         <v>59.65</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J18" s="4">
         <v>6.9</v>
@@ -1478,7 +1447,7 @@
         <v>23.6</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
@@ -1486,28 +1455,28 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D19" s="4">
         <v>47.67</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F19" s="4">
         <v>39.93</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H19" s="4">
         <v>61.4</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J19" s="4">
         <v>5.9</v>
@@ -1519,7 +1488,7 @@
         <v>23.1</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
@@ -1527,28 +1496,28 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="D20" s="4">
         <v>68.17</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F20" s="4">
         <v>41.6</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H20" s="4">
         <v>81.97</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J20" s="4">
         <v>7.2</v>
@@ -1560,7 +1529,7 @@
         <v>23.4</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
@@ -1568,28 +1537,28 @@
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="D21" s="4">
         <v>63.62</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F21" s="4">
         <v>31.88</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H21" s="4">
         <v>78.989999999999995</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J21" s="4">
         <v>5.9</v>
@@ -1601,7 +1570,7 @@
         <v>22.3</v>
       </c>
       <c r="M21" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
@@ -1609,28 +1578,28 @@
         <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D22" s="4">
         <v>52.43</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F22" s="4">
         <v>43.39</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H22" s="4">
         <v>74.72</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J22" s="4">
         <v>6.7</v>
@@ -1642,7 +1611,7 @@
         <v>23.9</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
@@ -1650,28 +1619,28 @@
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D23" s="4">
         <v>57.22</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F23" s="4">
         <v>33.4</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H23" s="4">
         <v>65.33</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J23" s="4">
         <v>6.2</v>
@@ -1683,7 +1652,7 @@
         <v>23.5</v>
       </c>
       <c r="M23" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
@@ -1691,28 +1660,28 @@
         <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D24" s="4">
         <v>41.82</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F24" s="4">
         <v>40.75</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H24" s="4">
         <v>65.84</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J24" s="4">
         <v>6.3</v>
@@ -1724,7 +1693,7 @@
         <v>22.9</v>
       </c>
       <c r="M24" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
@@ -1732,28 +1701,28 @@
         <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="D25" s="4">
         <v>37.340000000000003</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F25" s="4">
         <v>33.729999999999997</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H25" s="4">
         <v>67.67</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J25" s="4">
         <v>5.8</v>
@@ -1765,172 +1734,56 @@
         <v>23.6</v>
       </c>
       <c r="M25" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="D26" s="4">
-        <v>43.16</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F26" s="4">
-        <v>37.47</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H26" s="4">
-        <v>54.69</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J26" s="4">
-        <v>6</v>
-      </c>
-      <c r="K26" s="4">
-        <v>74.599999999999994</v>
-      </c>
-      <c r="L26" s="4">
-        <v>23.9</v>
-      </c>
-      <c r="M26" s="4" t="s">
-        <v>45</v>
-      </c>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D27" s="4">
-        <v>53.23</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F27" s="4">
-        <v>31.44</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H27" s="4">
-        <v>67.42</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J27" s="4">
-        <v>6.3</v>
-      </c>
-      <c r="K27" s="4">
-        <v>73.599999999999994</v>
-      </c>
-      <c r="L27" s="4">
-        <v>23.7</v>
-      </c>
-      <c r="M27" s="4" t="s">
-        <v>45</v>
-      </c>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="D28" s="4">
-        <v>54.47</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F28" s="4">
-        <v>32.950000000000003</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H28" s="4">
-        <v>59.36</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J28" s="4">
-        <v>5.9</v>
-      </c>
-      <c r="K28" s="4">
-        <v>78</v>
-      </c>
-      <c r="L28" s="4">
-        <v>22.8</v>
-      </c>
-      <c r="M28" s="4" t="s">
-        <v>45</v>
-      </c>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="6"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D29" s="4">
-        <v>39.72</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F29" s="4">
-        <v>39.83</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H29" s="4">
-        <v>55.33</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J29" s="4">
-        <v>6.5</v>
-      </c>
-      <c r="K29" s="4">
-        <v>77.7</v>
-      </c>
-      <c r="L29" s="4">
-        <v>23.5</v>
-      </c>
-      <c r="M29" s="4" t="s">
-        <v>45</v>
-      </c>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Dataset2.xlsx
+++ b/Dataset2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MyBook Z Series\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kuliah\Semester 6\Visualisasi Informasi\Syntax\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29A2431C-C8DC-48D4-AEAD-47838D933741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{942E83E8-4F63-4606-A2C0-1171E94C5380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0EAB97F0-0957-4D9B-B7FD-20E7CE86B6C9}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="88">
   <si>
     <t>T1</t>
   </si>
@@ -138,12 +138,6 @@
     <t>Jenis_Komoditas</t>
   </si>
   <si>
-    <t>Sedang</t>
-  </si>
-  <si>
-    <t>Tinggi</t>
-  </si>
-  <si>
     <t>Caisim</t>
   </si>
   <si>
@@ -151,9 +145,6 @@
   </si>
   <si>
     <t>Singkong</t>
-  </si>
-  <si>
-    <t>Rendah</t>
   </si>
   <si>
     <t>7°20'31.55"</t>
@@ -363,7 +354,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -377,6 +368,9 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -758,28 +752,31 @@
         <v>0</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D2" s="4">
         <v>86.98</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>37</v>
+      <c r="E2" s="4" t="str">
+        <f>_xlfn.IFS(D2&lt;40, "Rendah", D2&lt;=60, "Sedang", D2&gt;60, "Tinggi")</f>
+        <v>Tinggi</v>
       </c>
       <c r="F2" s="4">
         <v>54.43</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>38</v>
+      <c r="G2" s="4" t="str">
+        <f>_xlfn.IFS(F2&lt;40, "Rendah", F2&lt;=60, "Sedang", F2&gt;60, "Tinggi")</f>
+        <v>Sedang</v>
       </c>
       <c r="H2" s="4">
         <v>79.39</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>38</v>
+      <c r="I2" s="4" t="str">
+        <f>_xlfn.IFS(H2&lt;40, "Rendah", H2&lt;=60, "Sedang", H2&gt;60, "Tinggi")</f>
+        <v>Tinggi</v>
       </c>
       <c r="J2" s="4">
         <v>6.9</v>
@@ -791,7 +788,7 @@
         <v>23.1</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -799,28 +796,31 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D3" s="4">
         <v>82.33</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>37</v>
+      <c r="E3" s="4" t="str">
+        <f t="shared" ref="E3:E25" si="0">_xlfn.IFS(D3&lt;40, "Rendah", D3&lt;=60, "Sedang", D3&gt;60, "Tinggi")</f>
+        <v>Tinggi</v>
       </c>
       <c r="F3" s="4">
         <v>47.03</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>38</v>
+      <c r="G3" s="4" t="str">
+        <f t="shared" ref="G3:G25" si="1">_xlfn.IFS(F3&lt;40, "Rendah", F3&lt;=60, "Sedang", F3&gt;60, "Tinggi")</f>
+        <v>Sedang</v>
       </c>
       <c r="H3" s="4">
         <v>87.02</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>38</v>
+      <c r="I3" s="4" t="str">
+        <f t="shared" ref="I3:I25" si="2">_xlfn.IFS(H3&lt;40, "Rendah", H3&lt;=60, "Sedang", H3&gt;60, "Tinggi")</f>
+        <v>Tinggi</v>
       </c>
       <c r="J3" s="4">
         <v>6.7</v>
@@ -832,7 +832,7 @@
         <v>22.9</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -840,28 +840,31 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D4" s="4">
         <v>73.260000000000005</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>37</v>
+      <c r="E4" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Tinggi</v>
       </c>
       <c r="F4" s="4">
         <v>38.119999999999997</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>37</v>
+      <c r="G4" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Rendah</v>
       </c>
       <c r="H4" s="4">
         <v>97.5</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>38</v>
+      <c r="I4" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>Tinggi</v>
       </c>
       <c r="J4" s="4">
         <v>6.4</v>
@@ -873,7 +876,7 @@
         <v>23.4</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
@@ -881,28 +884,31 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D5" s="4">
         <v>91.24</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>37</v>
+      <c r="E5" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Tinggi</v>
       </c>
       <c r="F5" s="4">
         <v>47.36</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>38</v>
+      <c r="G5" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Sedang</v>
       </c>
       <c r="H5" s="4">
         <v>90.67</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>38</v>
+      <c r="I5" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>Tinggi</v>
       </c>
       <c r="J5" s="4">
         <v>6.3</v>
@@ -914,7 +920,7 @@
         <v>22.4</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
@@ -922,28 +928,31 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D6" s="4">
         <v>86.52</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>37</v>
+      <c r="E6" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Tinggi</v>
       </c>
       <c r="F6" s="4">
         <v>50.65</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>38</v>
+      <c r="G6" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Sedang</v>
       </c>
       <c r="H6" s="4">
         <v>83.92</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>38</v>
+      <c r="I6" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>Tinggi</v>
       </c>
       <c r="J6" s="4">
         <v>6.4</v>
@@ -955,7 +964,7 @@
         <v>22.2</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
@@ -963,28 +972,31 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D7" s="4">
         <v>93.77</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>37</v>
+      <c r="E7" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Tinggi</v>
       </c>
       <c r="F7" s="4">
         <v>48.86</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>38</v>
+      <c r="G7" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Sedang</v>
       </c>
       <c r="H7" s="4">
         <v>94.9</v>
       </c>
-      <c r="I7" s="4" t="s">
-        <v>38</v>
+      <c r="I7" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>Tinggi</v>
       </c>
       <c r="J7" s="4">
         <v>6.5</v>
@@ -996,7 +1008,7 @@
         <v>23.1</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
@@ -1004,28 +1016,31 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D8" s="4">
         <v>81.5</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>37</v>
+      <c r="E8" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Tinggi</v>
       </c>
       <c r="F8" s="4">
         <v>45.64</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>38</v>
+      <c r="G8" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Sedang</v>
       </c>
       <c r="H8" s="4">
         <v>80.83</v>
       </c>
-      <c r="I8" s="4" t="s">
-        <v>38</v>
+      <c r="I8" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>Tinggi</v>
       </c>
       <c r="J8" s="4">
         <v>7</v>
@@ -1037,7 +1052,7 @@
         <v>22.1</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
@@ -1045,28 +1060,31 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D9" s="4">
         <v>94.24</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>37</v>
+      <c r="E9" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Tinggi</v>
       </c>
       <c r="F9" s="4">
         <v>41.96</v>
       </c>
-      <c r="G9" s="4" t="s">
-        <v>38</v>
+      <c r="G9" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Sedang</v>
       </c>
       <c r="H9" s="4">
         <v>76.28</v>
       </c>
-      <c r="I9" s="4" t="s">
-        <v>38</v>
+      <c r="I9" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>Tinggi</v>
       </c>
       <c r="J9" s="4">
         <v>6.2</v>
@@ -1078,7 +1096,7 @@
         <v>22.7</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
@@ -1086,28 +1104,31 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D10" s="4">
         <v>80.88</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>37</v>
+      <c r="E10" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Tinggi</v>
       </c>
       <c r="F10" s="4">
         <v>45.13</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>38</v>
+      <c r="G10" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Sedang</v>
       </c>
       <c r="H10" s="4">
         <v>94.54</v>
       </c>
-      <c r="I10" s="4" t="s">
-        <v>38</v>
+      <c r="I10" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>Tinggi</v>
       </c>
       <c r="J10" s="4">
         <v>6.4</v>
@@ -1119,7 +1140,7 @@
         <v>23.7</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
@@ -1127,28 +1148,31 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D11" s="4">
         <v>77.430000000000007</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>37</v>
+      <c r="E11" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Tinggi</v>
       </c>
       <c r="F11" s="4">
         <v>52.43</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>38</v>
+      <c r="G11" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Sedang</v>
       </c>
       <c r="H11" s="4">
         <v>81.88</v>
       </c>
-      <c r="I11" s="4" t="s">
-        <v>38</v>
+      <c r="I11" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>Tinggi</v>
       </c>
       <c r="J11" s="4">
         <v>6.5</v>
@@ -1160,7 +1184,7 @@
         <v>23.9</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
@@ -1168,28 +1192,31 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D12" s="4">
         <v>93.16</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>37</v>
+      <c r="E12" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Tinggi</v>
       </c>
       <c r="F12" s="4">
         <v>42.57</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>38</v>
+      <c r="G12" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Sedang</v>
       </c>
       <c r="H12" s="4">
         <v>83.09</v>
       </c>
-      <c r="I12" s="4" t="s">
-        <v>38</v>
+      <c r="I12" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>Tinggi</v>
       </c>
       <c r="J12" s="4">
         <v>6.1</v>
@@ -1201,7 +1228,7 @@
         <v>23.4</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
@@ -1209,28 +1236,31 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D13" s="4">
         <v>68.7</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>37</v>
+      <c r="E13" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Tinggi</v>
       </c>
       <c r="F13" s="4">
         <v>36.94</v>
       </c>
-      <c r="G13" s="4" t="s">
-        <v>37</v>
+      <c r="G13" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Rendah</v>
       </c>
       <c r="H13" s="4">
         <v>83.83</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>38</v>
+      <c r="I13" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>Tinggi</v>
       </c>
       <c r="J13" s="4">
         <v>6.2</v>
@@ -1242,7 +1272,7 @@
         <v>23.2</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
@@ -1250,28 +1280,31 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D14" s="4">
         <v>48.4</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>37</v>
+      <c r="E14" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Sedang</v>
       </c>
       <c r="F14" s="4">
         <v>36.07</v>
       </c>
-      <c r="G14" s="4" t="s">
-        <v>37</v>
+      <c r="G14" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Rendah</v>
       </c>
       <c r="H14" s="4">
         <v>80.349999999999994</v>
       </c>
-      <c r="I14" s="4" t="s">
-        <v>38</v>
+      <c r="I14" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>Tinggi</v>
       </c>
       <c r="J14" s="4">
         <v>6</v>
@@ -1283,7 +1316,7 @@
         <v>22.9</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
@@ -1291,28 +1324,31 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D15" s="4">
         <v>65.400000000000006</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>37</v>
+      <c r="E15" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Tinggi</v>
       </c>
       <c r="F15" s="4">
         <v>41.98</v>
       </c>
-      <c r="G15" s="4" t="s">
-        <v>38</v>
+      <c r="G15" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Sedang</v>
       </c>
       <c r="H15" s="4">
         <v>55.36</v>
       </c>
-      <c r="I15" s="4" t="s">
-        <v>38</v>
+      <c r="I15" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>Sedang</v>
       </c>
       <c r="J15" s="4">
         <v>6.3</v>
@@ -1324,7 +1360,7 @@
         <v>22.5</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
@@ -1332,28 +1368,31 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D16" s="4">
         <v>60.35</v>
       </c>
-      <c r="E16" s="4" t="s">
-        <v>37</v>
+      <c r="E16" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Tinggi</v>
       </c>
       <c r="F16" s="4">
         <v>47.6</v>
       </c>
-      <c r="G16" s="4" t="s">
-        <v>38</v>
+      <c r="G16" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Sedang</v>
       </c>
       <c r="H16" s="4">
         <v>80.400000000000006</v>
       </c>
-      <c r="I16" s="4" t="s">
-        <v>38</v>
+      <c r="I16" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>Tinggi</v>
       </c>
       <c r="J16" s="4">
         <v>7.5</v>
@@ -1365,7 +1404,7 @@
         <v>22.9</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
@@ -1373,28 +1412,31 @@
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D17" s="4">
         <v>64.55</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>37</v>
+      <c r="E17" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Tinggi</v>
       </c>
       <c r="F17" s="4">
         <v>36.47</v>
       </c>
-      <c r="G17" s="4" t="s">
-        <v>37</v>
+      <c r="G17" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Rendah</v>
       </c>
       <c r="H17" s="4">
         <v>75.069999999999993</v>
       </c>
-      <c r="I17" s="4" t="s">
-        <v>38</v>
+      <c r="I17" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>Tinggi</v>
       </c>
       <c r="J17" s="4">
         <v>7.4</v>
@@ -1406,7 +1448,7 @@
         <v>22.6</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
@@ -1414,28 +1456,31 @@
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D18" s="4">
         <v>50.59</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>37</v>
+      <c r="E18" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Sedang</v>
       </c>
       <c r="F18" s="4">
         <v>46.84</v>
       </c>
-      <c r="G18" s="4" t="s">
-        <v>38</v>
+      <c r="G18" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Sedang</v>
       </c>
       <c r="H18" s="4">
         <v>59.65</v>
       </c>
-      <c r="I18" s="4" t="s">
-        <v>38</v>
+      <c r="I18" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>Sedang</v>
       </c>
       <c r="J18" s="4">
         <v>6.9</v>
@@ -1447,7 +1492,7 @@
         <v>23.6</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
@@ -1455,28 +1500,31 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D19" s="4">
         <v>47.67</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>37</v>
+      <c r="E19" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Sedang</v>
       </c>
       <c r="F19" s="4">
         <v>39.93</v>
       </c>
-      <c r="G19" s="4" t="s">
-        <v>37</v>
+      <c r="G19" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Rendah</v>
       </c>
       <c r="H19" s="4">
         <v>61.4</v>
       </c>
-      <c r="I19" s="4" t="s">
-        <v>38</v>
+      <c r="I19" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>Tinggi</v>
       </c>
       <c r="J19" s="4">
         <v>5.9</v>
@@ -1488,7 +1536,7 @@
         <v>23.1</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
@@ -1496,28 +1544,31 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D20" s="4">
         <v>68.17</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>37</v>
+      <c r="E20" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Tinggi</v>
       </c>
       <c r="F20" s="4">
         <v>41.6</v>
       </c>
-      <c r="G20" s="4" t="s">
-        <v>38</v>
+      <c r="G20" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Sedang</v>
       </c>
       <c r="H20" s="4">
         <v>81.97</v>
       </c>
-      <c r="I20" s="4" t="s">
-        <v>38</v>
+      <c r="I20" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>Tinggi</v>
       </c>
       <c r="J20" s="4">
         <v>7.2</v>
@@ -1529,7 +1580,7 @@
         <v>23.4</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
@@ -1537,28 +1588,31 @@
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D21" s="4">
         <v>63.62</v>
       </c>
-      <c r="E21" s="4" t="s">
-        <v>37</v>
+      <c r="E21" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Tinggi</v>
       </c>
       <c r="F21" s="4">
         <v>31.88</v>
       </c>
-      <c r="G21" s="4" t="s">
-        <v>37</v>
+      <c r="G21" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Rendah</v>
       </c>
       <c r="H21" s="4">
         <v>78.989999999999995</v>
       </c>
-      <c r="I21" s="4" t="s">
-        <v>38</v>
+      <c r="I21" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>Tinggi</v>
       </c>
       <c r="J21" s="4">
         <v>5.9</v>
@@ -1570,7 +1624,7 @@
         <v>22.3</v>
       </c>
       <c r="M21" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
@@ -1578,28 +1632,31 @@
         <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D22" s="4">
         <v>52.43</v>
       </c>
-      <c r="E22" s="4" t="s">
-        <v>37</v>
+      <c r="E22" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Sedang</v>
       </c>
       <c r="F22" s="4">
         <v>43.39</v>
       </c>
-      <c r="G22" s="4" t="s">
-        <v>38</v>
+      <c r="G22" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Sedang</v>
       </c>
       <c r="H22" s="4">
         <v>74.72</v>
       </c>
-      <c r="I22" s="4" t="s">
-        <v>38</v>
+      <c r="I22" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>Tinggi</v>
       </c>
       <c r="J22" s="4">
         <v>6.7</v>
@@ -1611,7 +1668,7 @@
         <v>23.9</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
@@ -1619,28 +1676,31 @@
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D23" s="4">
         <v>57.22</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>37</v>
+      <c r="E23" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Sedang</v>
       </c>
       <c r="F23" s="4">
         <v>33.4</v>
       </c>
-      <c r="G23" s="4" t="s">
-        <v>37</v>
+      <c r="G23" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Rendah</v>
       </c>
       <c r="H23" s="4">
         <v>65.33</v>
       </c>
-      <c r="I23" s="4" t="s">
-        <v>38</v>
+      <c r="I23" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>Tinggi</v>
       </c>
       <c r="J23" s="4">
         <v>6.2</v>
@@ -1652,7 +1712,7 @@
         <v>23.5</v>
       </c>
       <c r="M23" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
@@ -1660,28 +1720,31 @@
         <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D24" s="4">
         <v>41.82</v>
       </c>
-      <c r="E24" s="4" t="s">
-        <v>37</v>
+      <c r="E24" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Sedang</v>
       </c>
       <c r="F24" s="4">
         <v>40.75</v>
       </c>
-      <c r="G24" s="4" t="s">
-        <v>38</v>
+      <c r="G24" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Sedang</v>
       </c>
       <c r="H24" s="4">
         <v>65.84</v>
       </c>
-      <c r="I24" s="4" t="s">
-        <v>38</v>
+      <c r="I24" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>Tinggi</v>
       </c>
       <c r="J24" s="4">
         <v>6.3</v>
@@ -1693,7 +1756,7 @@
         <v>22.9</v>
       </c>
       <c r="M24" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
@@ -1701,28 +1764,31 @@
         <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D25" s="4">
         <v>37.340000000000003</v>
       </c>
-      <c r="E25" s="4" t="s">
-        <v>42</v>
+      <c r="E25" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>Rendah</v>
       </c>
       <c r="F25" s="4">
         <v>33.729999999999997</v>
       </c>
-      <c r="G25" s="4" t="s">
-        <v>37</v>
+      <c r="G25" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Rendah</v>
       </c>
       <c r="H25" s="4">
         <v>67.67</v>
       </c>
-      <c r="I25" s="4" t="s">
-        <v>38</v>
+      <c r="I25" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>Tinggi</v>
       </c>
       <c r="J25" s="4">
         <v>5.8</v>
@@ -1734,7 +1800,7 @@
         <v>23.6</v>
       </c>
       <c r="M25" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
@@ -1744,7 +1810,7 @@
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
-      <c r="J26" s="6"/>
+      <c r="J26" s="7"/>
       <c r="K26" s="6"/>
       <c r="L26" s="6"/>
       <c r="M26" s="6"/>
